--- a/data/risk_of_bias_rob2.xlsx
+++ b/data/risk_of_bias_rob2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58393CBD-17A6-004E-AF82-6EEF8CBB65DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF90E3C8-E6F9-3F47-9FAE-913362625C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15280" yWindow="980" windowWidth="13280" windowHeight="15640" xr2:uid="{796BC763-D08A-9149-9790-F72E91794F1A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{796BC763-D08A-9149-9790-F72E91794F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,7 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
@@ -645,7 +645,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>33</v>
@@ -668,7 +668,7 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
@@ -691,10 +691,10 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -941,7 +941,7 @@
         <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>33</v>
@@ -953,7 +953,7 @@
         <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1134,10 +1134,10 @@
         <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/risk_of_bias_rob2.xlsx
+++ b/data/risk_of_bias_rob2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF90E3C8-E6F9-3F47-9FAE-913362625C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBF93D4-B8D1-5442-872A-735D51F61BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{796BC763-D08A-9149-9790-F72E91794F1A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{796BC763-D08A-9149-9790-F72E91794F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="35">
   <si>
     <t>Study</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>Waller et al. (2022)</t>
-  </si>
-  <si>
-    <t>Li et al. (2024)</t>
   </si>
   <si>
     <t>Allen et al. (2022)</t>
@@ -531,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55374DB-C33D-2C40-AF77-54A6CF9D7244}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -547,22 +544,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -570,22 +567,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -593,22 +590,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -616,22 +613,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -639,45 +636,45 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -685,22 +682,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -708,22 +705,22 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -731,22 +728,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -754,22 +751,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -777,22 +774,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -800,22 +797,22 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -823,22 +820,22 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -846,22 +843,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -869,22 +866,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -892,22 +889,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -915,22 +912,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -938,22 +935,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -961,22 +958,22 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -984,22 +981,22 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1007,22 +1004,22 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1030,65 +1027,65 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24" t="s">
         <v>31</v>
@@ -1099,45 +1096,22 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/risk_of_bias_rob2.xlsx
+++ b/data/risk_of_bias_rob2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramanaye/Documents/GitHub/cancer_nutrition_evidence_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBF93D4-B8D1-5442-872A-735D51F61BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1C5BEA-CF3F-4E46-9E00-35CAE6E09889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{796BC763-D08A-9149-9790-F72E91794F1A}"/>
+    <workbookView xWindow="14260" yWindow="500" windowWidth="14540" windowHeight="16140" xr2:uid="{796BC763-D08A-9149-9790-F72E91794F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -777,7 +777,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>30</v>
@@ -846,19 +846,19 @@
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
         <v>29</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -872,7 +872,7 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
@@ -1076,7 +1076,7 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
@@ -1088,7 +1088,7 @@
         <v>29</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
